--- a/Input Hopfner.xlsx
+++ b/Input Hopfner.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\martinahopfner.github.io\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://almquistarchitectureagency-my.sharepoint.com/personal/henrik_a-a-a_se/Documents/AAA/03_COM/_WEB/Martinas web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{636A62C4-4DCF-463D-8F70-42C2AB8EEDF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="8_{EA8D6A7D-AABD-41A9-B8B8-999DFAF428CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E2BC88F-E88D-41CA-813E-EDF6BD4FEACC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" xr2:uid="{5BA2C9A2-01C8-41FE-A486-6418B9B1B1A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="63">
   <si>
     <t>img</t>
   </si>
@@ -56,16 +56,10 @@
     <t>y</t>
   </si>
   <si>
-    <t>hopfner-01.png</t>
-  </si>
-  <si>
-    <t>Fer</t>
-  </si>
-  <si>
-    <t>hopfner-02.png</t>
-  </si>
-  <si>
-    <t>Silhouette and Backbone</t>
+    <t>mobile</t>
+  </si>
+  <si>
+    <t>comment</t>
   </si>
   <si>
     <t>in percentage
@@ -75,18 +69,187 @@
 plus y - up</t>
   </si>
   <si>
-    <t>comment</t>
+    <t>mobile
+1 - portait to show
+0 - landscape to not show</t>
+  </si>
+  <si>
+    <t>Fer - A Beauty Story</t>
   </si>
   <si>
     <t>Photo: Denny Sachtleben
 Hair: Masayuki Yuasa
-Make up: Lee Hyangsoon
+Make-up: Lee Hyangsoon
 Styling: Kalle Hildinger
 Model: Fernanda Zilio | Louisa Models</t>
   </si>
   <si>
+    <t>Hair Story</t>
+  </si>
+  <si>
     <t>Photo: Denny Sachtleben
-Set: Cathrin Sonntag</t>
+Hair Sculpting: Cathrin Sonntag
+Model: Henrik Almquist</t>
+  </si>
+  <si>
+    <t>Photo: Denny Sachtleben
+Prop Styling: Cathrin Sonntag
+Model: Henrik Almquist</t>
+  </si>
+  <si>
+    <t>Silhouette &amp; Backbone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photo: Kornelia Konieczka
+Styling: Rhea Fey
+H+M: Carolin Jarchow
+Set: Theresa Rohé
+Light: Nina Petrova
+Model: Michelle Laff
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photo: Kornelia Konieczka
+Set: Theresa Rohé
+</t>
+  </si>
+  <si>
+    <t>Skin Vestige</t>
+  </si>
+  <si>
+    <t>Photo: Denny Sachtleben
+Styling: Camille Franke
+Set: Cathrin Sonntag
+Model: Feng Liang Guo</t>
+  </si>
+  <si>
+    <t>Soul</t>
+  </si>
+  <si>
+    <t>Scan: Cathrin Sonntag</t>
+  </si>
+  <si>
+    <t>Fer_01.jpg</t>
+  </si>
+  <si>
+    <t>Fer_02.jpg</t>
+  </si>
+  <si>
+    <t>Fer_03.jpg</t>
+  </si>
+  <si>
+    <t>Fer_04.jpg</t>
+  </si>
+  <si>
+    <t>Fer_05.jpg</t>
+  </si>
+  <si>
+    <t>Fer_06.jpg</t>
+  </si>
+  <si>
+    <t>Fer_07.jpg</t>
+  </si>
+  <si>
+    <t>Fer_08.jpg</t>
+  </si>
+  <si>
+    <t>Fer_09.jpg</t>
+  </si>
+  <si>
+    <t>Hair-Story_01.jpg</t>
+  </si>
+  <si>
+    <t>Hair-Story_02.jpg</t>
+  </si>
+  <si>
+    <t>Hair-Story_03.jpg</t>
+  </si>
+  <si>
+    <t>Hair-Story_04.jpg</t>
+  </si>
+  <si>
+    <t>Hair-Story_05.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_01.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_02.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_03.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_04.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_05.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_06.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_07.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_08.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_09.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_10.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_11.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_12.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_13.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_14.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_15.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_16.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_17.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_18.jpg</t>
+  </si>
+  <si>
+    <t>Silhouette-and-backbone_19.jpg</t>
+  </si>
+  <si>
+    <t>Skin-Vestige_01.jpg</t>
+  </si>
+  <si>
+    <t>Skin-Vestige_02.jpg</t>
+  </si>
+  <si>
+    <t>Skin-Vestige_03.jpg</t>
+  </si>
+  <si>
+    <t>Skin-Vestige_04.jpg</t>
+  </si>
+  <si>
+    <t>Skin-Vestige_05.jpg</t>
+  </si>
+  <si>
+    <t>Soul_01.jpg</t>
+  </si>
+  <si>
+    <t>Soul_02.jpg</t>
+  </si>
+  <si>
+    <t>Soul_03.jpg</t>
   </si>
 </sst>
 </file>
@@ -136,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -149,6 +312,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,14 +656,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785963ED-F8C1-409E-94A9-D6B12E43F30E}">
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="30.6328125" customWidth="1"/>
-    <col min="8" max="8" width="30.6328125" style="1" customWidth="1"/>
+    <col min="1" max="3" width="30.54296875" customWidth="1"/>
+    <col min="4" max="4" width="30.54296875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="33.26953125" customWidth="1"/>
+    <col min="8" max="8" width="30.54296875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -501,7 +675,7 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -510,411 +684,1040 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3"/>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="87" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E2" s="2">
         <v>0</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
       </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
       <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="D11" s="6"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="D17" s="6"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17" s="2"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2">
+        <v>1</v>
+      </c>
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2">
+        <v>1</v>
+      </c>
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" spans="1:9" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
+      <c r="D37" s="6"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G37" s="2"/>
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0</v>
+      </c>
+      <c r="G41" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
+      <c r="D43" s="6"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2">
+        <v>0</v>
+      </c>
+      <c r="G44" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0</v>
+      </c>
+      <c r="G45" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
+      <c r="D47" s="6"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="D48" s="6"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
     </row>
@@ -922,7 +1725,7 @@
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
+      <c r="D49" s="6"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
     </row>
@@ -930,7 +1733,7 @@
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="D50" s="6"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
     </row>
@@ -938,7 +1741,7 @@
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
+      <c r="D51" s="6"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
     </row>
@@ -946,7 +1749,7 @@
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+      <c r="D52" s="6"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
     </row>
@@ -954,7 +1757,7 @@
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
+      <c r="D53" s="6"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
     </row>
@@ -962,7 +1765,7 @@
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+      <c r="D54" s="6"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
     </row>
@@ -970,41 +1773,9 @@
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
+      <c r="D55" s="6"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Input Hopfner.xlsx
+++ b/Input Hopfner.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://almquistarchitectureagency-my.sharepoint.com/personal/henrik_a-a-a_se/Documents/AAA/03_COM/_WEB/Martinas web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="274" documentId="8_{EA8D6A7D-AABD-41A9-B8B8-999DFAF428CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49F6B065-50C5-461D-8C64-291C879E7639}"/>
+  <xr:revisionPtr revIDLastSave="275" documentId="8_{EA8D6A7D-AABD-41A9-B8B8-999DFAF428CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE90DA9E-6A45-4AC3-8528-BA8F900B18F8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" xr2:uid="{5BA2C9A2-01C8-41FE-A486-6418B9B1B1A5}"/>
   </bookViews>
@@ -945,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9">

--- a/Input Hopfner.xlsx
+++ b/Input Hopfner.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://almquistarchitectureagency-my.sharepoint.com/personal/henrik_a-a-a_se/Documents/AAA/03_COM/_WEB/Martinas web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="275" documentId="8_{EA8D6A7D-AABD-41A9-B8B8-999DFAF428CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE90DA9E-6A45-4AC3-8528-BA8F900B18F8}"/>
+  <xr:revisionPtr revIDLastSave="304" documentId="8_{EA8D6A7D-AABD-41A9-B8B8-999DFAF428CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{190D1EC5-C61C-4A77-BE16-582FB2101393}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" xr2:uid="{5BA2C9A2-01C8-41FE-A486-6418B9B1B1A5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="53">
   <si>
     <t>img</t>
   </si>
@@ -114,6 +114,10 @@
     <t>Hair Story</t>
   </si>
   <si>
+    <t>Hair Story
+Editorial for Bound Magazine</t>
+  </si>
+  <si>
     <t>Photo: Denny Sachtleben
 Hair Sculpting: Cathrin Sonntag
 Model: Henrik Almquist</t>
@@ -136,6 +140,10 @@
   </si>
   <si>
     <t>Silhouette &amp; Backbone</t>
+  </si>
+  <si>
+    <t>Silhouette &amp; Backbone
+Editorial for VOGUE Portugal</t>
   </si>
   <si>
     <t xml:space="preserve">Photo: Kornelia Konieczka
@@ -619,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785963ED-F8C1-409E-94A9-D6B12E43F30E}">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="3" width="30.5703125" customWidth="1"/>
@@ -861,10 +869,10 @@
         <v>21</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2">
         <v>0</v>
@@ -878,16 +886,16 @@
     </row>
     <row r="12" spans="1:9" ht="69.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E12" s="2">
         <v>0</v>
@@ -904,16 +912,16 @@
     </row>
     <row r="13" spans="1:9" ht="69.75" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -927,16 +935,16 @@
     </row>
     <row r="14" spans="1:9" ht="69.75" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -960,16 +968,16 @@
     </row>
     <row r="16" spans="1:9" ht="99.75" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
@@ -984,16 +992,16 @@
     </row>
     <row r="17" spans="1:9" ht="99.75" customHeight="1">
       <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="D17" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2">
         <v>0</v>
@@ -1008,16 +1016,16 @@
     </row>
     <row r="18" spans="1:9" ht="45" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2">
         <v>0</v>
@@ -1032,16 +1040,16 @@
     </row>
     <row r="19" spans="1:9" ht="99.75" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2">
         <v>0</v>
@@ -1056,16 +1064,16 @@
     </row>
     <row r="20" spans="1:9" ht="99.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2">
         <v>0</v>
@@ -1080,16 +1088,16 @@
     </row>
     <row r="21" spans="1:9" ht="99.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2">
         <v>0</v>
@@ -1104,16 +1112,16 @@
     </row>
     <row r="22" spans="1:9" ht="99.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
@@ -1128,16 +1136,16 @@
     </row>
     <row r="23" spans="1:9" ht="99.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
@@ -1152,16 +1160,16 @@
     </row>
     <row r="24" spans="1:9" ht="99.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
@@ -1176,16 +1184,16 @@
     </row>
     <row r="25" spans="1:9" ht="99.75" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E25" s="2">
         <v>0</v>
@@ -1200,16 +1208,16 @@
     </row>
     <row r="26" spans="1:9" ht="99.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E26" s="2">
         <v>0</v>
@@ -1224,16 +1232,16 @@
     </row>
     <row r="27" spans="1:9" ht="99.75" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E27" s="2">
         <v>0</v>
@@ -1258,16 +1266,16 @@
     </row>
     <row r="29" spans="1:9" ht="75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E29" s="2">
         <v>0</v>
@@ -1281,16 +1289,16 @@
     </row>
     <row r="30" spans="1:9" ht="75" customHeight="1">
       <c r="A30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="C30" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E30" s="2">
         <v>0</v>
@@ -1304,16 +1312,16 @@
     </row>
     <row r="31" spans="1:9" ht="75" customHeight="1">
       <c r="A31" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="E31" s="2">
         <v>0</v>
@@ -1327,16 +1335,16 @@
     </row>
     <row r="32" spans="1:9" ht="75" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E32" s="2">
         <v>0</v>
@@ -1357,18 +1365,18 @@
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="1:7" ht="15">
+    <row r="34" spans="1:7">
       <c r="A34" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E34" s="2">
         <v>0</v>
@@ -1452,15 +1460,6 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="1:7" ht="15"/>
-    <row r="45" spans="1:7" ht="15"/>
-    <row r="46" spans="1:7" ht="15"/>
-    <row r="47" spans="1:7" ht="15"/>
-    <row r="48" spans="1:7" ht="15"/>
-    <row r="49" ht="15"/>
-    <row r="50" ht="15"/>
-    <row r="53" ht="15"/>
-    <row r="54" ht="15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Input Hopfner.xlsx
+++ b/Input Hopfner.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://almquistarchitectureagency-my.sharepoint.com/personal/henrik_a-a-a_se/Documents/AAA/03_COM/_WEB/Martinas web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="304" documentId="8_{EA8D6A7D-AABD-41A9-B8B8-999DFAF428CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{190D1EC5-C61C-4A77-BE16-582FB2101393}"/>
+  <xr:revisionPtr revIDLastSave="343" documentId="8_{EA8D6A7D-AABD-41A9-B8B8-999DFAF428CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E16230F-7ECD-4073-B62D-A2973B9271CE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" xr2:uid="{5BA2C9A2-01C8-41FE-A486-6418B9B1B1A5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
   <si>
     <t>img</t>
   </si>
@@ -221,6 +221,38 @@
   </si>
   <si>
     <t>Scan: Cathrin Sonntag</t>
+  </si>
+  <si>
+    <t>Nymph_01</t>
+  </si>
+  <si>
+    <t>Nymph</t>
+  </si>
+  <si>
+    <t>Photo: Marry Rozzi
+Styling: Sara Medali
+Hair: Yui Ozaki
+Makeup: Kana Ohira
+Set: Raphaëlle Daguerre
+Model: Lena Ballayre | New Wave Management</t>
+  </si>
+  <si>
+    <t>Nymph_02</t>
+  </si>
+  <si>
+    <t>Photo: Marry Rozzi
+Styling: Sara Medali
+Set: Raphaëlle Daguerre</t>
+  </si>
+  <si>
+    <t>Nymph_03</t>
+  </si>
+  <si>
+    <t>Nymph_04</t>
+  </si>
+  <si>
+    <t>Photo: Marry Rozzi
+Set: Raphaëlle Daguerre</t>
   </si>
 </sst>
 </file>
@@ -270,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -292,6 +324,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1396,37 +1434,97 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
+    <row r="36" spans="1:7" ht="120" customHeight="1">
+      <c r="A36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0</v>
+      </c>
+      <c r="F36" s="8">
+        <v>0</v>
+      </c>
+      <c r="G36" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="120" customHeight="1">
+      <c r="A37" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8">
+        <v>0</v>
+      </c>
+      <c r="G37" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="120" customHeight="1">
+      <c r="A38" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0</v>
+      </c>
+      <c r="F38" s="8">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="120" customHeight="1">
+      <c r="A39" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0</v>
+      </c>
+      <c r="F39" s="8">
+        <v>0</v>
+      </c>
+      <c r="G39" s="9">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="2"/>

--- a/Input Hopfner.xlsx
+++ b/Input Hopfner.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://almquistarchitectureagency-my.sharepoint.com/personal/henrik_a-a-a_se/Documents/AAA/03_COM/_WEB/Martinas web/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heal_\Documents\GitHub\martinahopfner.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="343" documentId="8_{EA8D6A7D-AABD-41A9-B8B8-999DFAF428CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E16230F-7ECD-4073-B62D-A2973B9271CE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC93BDA-CB60-4499-BCBF-E7C221C2D560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" xr2:uid="{5BA2C9A2-01C8-41FE-A486-6418B9B1B1A5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="59">
   <si>
     <t>img</t>
   </si>
@@ -111,9 +111,6 @@
     <t>Hair-Story_01.jpg</t>
   </si>
   <si>
-    <t>Hair Story</t>
-  </si>
-  <si>
     <t>Hair Story
 Editorial for Bound Magazine</t>
   </si>
@@ -137,9 +134,6 @@
   </si>
   <si>
     <t>Silhouette-and-backbone_01.jpg</t>
-  </si>
-  <si>
-    <t>Silhouette &amp; Backbone</t>
   </si>
   <si>
     <t>Silhouette &amp; Backbone
@@ -223,12 +217,6 @@
     <t>Scan: Cathrin Sonntag</t>
   </si>
   <si>
-    <t>Nymph_01</t>
-  </si>
-  <si>
-    <t>Nymph</t>
-  </si>
-  <si>
     <t>Photo: Marry Rozzi
 Styling: Sara Medali
 Hair: Yui Ozaki
@@ -237,29 +225,36 @@
 Model: Lena Ballayre | New Wave Management</t>
   </si>
   <si>
-    <t>Nymph_02</t>
-  </si>
-  <si>
     <t>Photo: Marry Rozzi
 Styling: Sara Medali
 Set: Raphaëlle Daguerre</t>
   </si>
   <si>
-    <t>Nymph_03</t>
-  </si>
-  <si>
-    <t>Nymph_04</t>
-  </si>
-  <si>
     <t>Photo: Marry Rozzi
 Set: Raphaëlle Daguerre</t>
+  </si>
+  <si>
+    <t>Nymph_01.jpg</t>
+  </si>
+  <si>
+    <t>Nymph_02.jpg</t>
+  </si>
+  <si>
+    <t>Nymph_03.jpg</t>
+  </si>
+  <si>
+    <t>Nymph_04.jpg</t>
+  </si>
+  <si>
+    <t>Nymph
+Editorial for Blumenhaus Magazine</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,7 +328,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -666,15 +661,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785963ED-F8C1-409E-94A9-D6B12E43F30E}">
   <dimension ref="A1:I43"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="30.5703125" customWidth="1"/>
+    <col min="1" max="3" width="30.54296875" customWidth="1"/>
     <col min="4" max="4" width="39" style="7" customWidth="1"/>
-    <col min="6" max="6" width="33.28515625" customWidth="1"/>
-    <col min="8" max="8" width="30.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="33.26953125" customWidth="1"/>
+    <col min="8" max="8" width="30.54296875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -700,7 +695,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="99.75" customHeight="1">
+    <row r="2" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -726,7 +721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="99.75" customHeight="1">
+    <row r="3" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -752,7 +747,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="99.75" customHeight="1">
+    <row r="4" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -775,7 +770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="99.75" customHeight="1">
+    <row r="5" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -798,7 +793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="99.75" customHeight="1">
+    <row r="6" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -821,7 +816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="99.75" customHeight="1">
+    <row r="7" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -844,7 +839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="99.75" customHeight="1">
+    <row r="8" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -867,7 +862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="99.75" customHeight="1">
+    <row r="9" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
@@ -890,7 +885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -899,7 +894,7 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="69.75" customHeight="1">
+    <row r="11" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -907,33 +902,33 @@
         <v>21</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="69.75" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2">
         <v>0</v>
@@ -948,19 +943,19 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="69.75" customHeight="1">
+    <row r="13" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="E13" s="2">
         <v>0</v>
       </c>
@@ -971,18 +966,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="69.75" customHeight="1">
+    <row r="14" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -994,7 +989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1004,282 +999,282 @@
       <c r="G15" s="2"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:9" ht="99.75" customHeight="1">
+    <row r="16" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="B17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" ht="99.75" customHeight="1">
-      <c r="A17" s="2" t="s">
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" ht="45" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" ht="99.75" customHeight="1">
-      <c r="A19" s="2" t="s">
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" ht="99.75" customHeight="1">
-      <c r="A20" s="2" t="s">
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="2">
-        <v>1</v>
-      </c>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9" ht="99.75" customHeight="1">
-      <c r="A21" s="2" t="s">
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1</v>
-      </c>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9" ht="99.75" customHeight="1">
-      <c r="A22" s="2" t="s">
+      <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2">
-        <v>1</v>
-      </c>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9" ht="99.75" customHeight="1">
-      <c r="A23" s="2" t="s">
+      <c r="E24" s="2">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" ht="99.75" customHeight="1">
-      <c r="A24" s="2" t="s">
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="2">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2">
-        <v>1</v>
-      </c>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" ht="99.75" customHeight="1">
-      <c r="A25" s="2" t="s">
+      <c r="E26" s="2">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="2">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2">
-        <v>1</v>
-      </c>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:9" ht="99.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="2">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9" ht="99.75" customHeight="1">
-      <c r="A27" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="B27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27" s="2">
         <v>0</v>
@@ -1292,7 +1287,7 @@
       </c>
       <c r="I27" s="2"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1302,87 +1297,87 @@
       <c r="G28" s="2"/>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:9" ht="75" customHeight="1">
+    <row r="29" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="6" t="s">
+      <c r="B30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="2">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="75" customHeight="1">
-      <c r="A30" s="2" t="s">
+      <c r="B31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E30" s="2">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="75" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" s="2">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="75" customHeight="1">
-      <c r="A32" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="B32" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E32" s="2">
         <v>0</v>
@@ -1394,7 +1389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -1403,19 +1398,19 @@
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>52</v>
-      </c>
       <c r="E34" s="2">
         <v>0</v>
       </c>
@@ -1426,7 +1421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1434,88 +1429,88 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:7" ht="120" customHeight="1">
+    <row r="36" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0</v>
+      </c>
+      <c r="F36" s="8">
+        <v>0</v>
+      </c>
+      <c r="G36" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8">
+        <v>0</v>
+      </c>
+      <c r="G37" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0</v>
+      </c>
+      <c r="F38" s="8">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0</v>
-      </c>
-      <c r="F36" s="8">
-        <v>0</v>
-      </c>
-      <c r="G36" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="120" customHeight="1">
-      <c r="A37" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0</v>
-      </c>
-      <c r="F37" s="8">
-        <v>0</v>
-      </c>
-      <c r="G37" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="120" customHeight="1">
-      <c r="A38" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0</v>
-      </c>
-      <c r="F38" s="8">
-        <v>0</v>
-      </c>
-      <c r="G38" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="120" customHeight="1">
-      <c r="A39" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="E39" s="8">
         <v>0</v>
       </c>
@@ -1526,7 +1521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -1534,7 +1529,7 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -1542,7 +1537,7 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -1550,7 +1545,7 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
